--- a/01-training-center-survey-analysis/data/master_table.xlsx
+++ b/01-training-center-survey-analysis/data/master_table.xlsx
@@ -923,7 +923,11 @@
       <c r="L8" t="n">
         <v>5</v>
       </c>
-      <c r="M8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>상담 신청을 남겼는데 운영팀에서 며칠째 확인을 안 하네요.</t>
+        </is>
+      </c>
       <c r="N8" t="b">
         <v>1</v>
       </c>
@@ -1283,7 +1287,11 @@
       <c r="L14" t="n">
         <v>4</v>
       </c>
-      <c r="M14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>갑작스러운 센터 휴관 공지가 너무 늦게 올라왔어요.</t>
+        </is>
+      </c>
       <c r="N14" t="b">
         <v>1</v>
       </c>
@@ -1583,7 +1591,11 @@
       <c r="L19" t="n">
         <v>5</v>
       </c>
-      <c r="M19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>와이파이가 자꾸 끊겨서 개인 노트북으로 작업하기 힘듭니다.</t>
+        </is>
+      </c>
       <c r="N19" t="b">
         <v>1</v>
       </c>
@@ -2915,7 +2927,11 @@
       <c r="L41" t="n">
         <v>5</v>
       </c>
-      <c r="M41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>안내문이 센터 내 잘 보이는 곳이 붙어 있으면 좋겠어요.</t>
+        </is>
+      </c>
       <c r="N41" t="b">
         <v>1</v>
       </c>
@@ -3831,7 +3847,11 @@
       <c r="L56" t="n">
         <v>4</v>
       </c>
-      <c r="M56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>예약 방법을 구체적으로 알려주세요</t>
+        </is>
+      </c>
       <c r="N56" t="b">
         <v>0</v>
       </c>
@@ -4195,7 +4215,11 @@
       <c r="L62" t="n">
         <v>4</v>
       </c>
-      <c r="M62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>화장실이 좀 더 깨끗하면 좋겠어요</t>
+        </is>
+      </c>
       <c r="N62" t="b">
         <v>0</v>
       </c>
@@ -4495,7 +4519,11 @@
       <c r="L67" t="n">
         <v>5</v>
       </c>
-      <c r="M67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>상담 신청을 남겼는데 운영팀에서 며칠째 확인을 안 하네요.</t>
+        </is>
+      </c>
       <c r="N67" t="b">
         <v>1</v>
       </c>
@@ -4743,7 +4771,11 @@
       <c r="L71" t="n">
         <v>4</v>
       </c>
-      <c r="M71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>강의실 조명이 너무 밝아서 화면을 볼 때 눈이 쉽게 피로해집니다.</t>
+        </is>
+      </c>
       <c r="N71" t="b">
         <v>0</v>
       </c>
@@ -5047,7 +5079,11 @@
       <c r="L76" t="n">
         <v>5</v>
       </c>
-      <c r="M76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>수강생 간의 친목 소음이 라운지에서 너무 크게 들립니다.</t>
+        </is>
+      </c>
       <c r="N76" t="b">
         <v>1</v>
       </c>
@@ -6087,7 +6123,11 @@
       <c r="L93" t="n">
         <v>5</v>
       </c>
-      <c r="M93" t="inlineStr"/>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>교육 프로그램 안내가 더 자주 나가면 좋을 것 같아요</t>
+        </is>
+      </c>
       <c r="N93" t="b">
         <v>1</v>
       </c>
@@ -6207,7 +6247,11 @@
       <c r="L95" t="n">
         <v>4</v>
       </c>
-      <c r="M95" t="inlineStr"/>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>강의실 조명이 너무 밝아서 화면을 볼 때 눈이 쉽게 피로해집니다.</t>
+        </is>
+      </c>
       <c r="N95" t="b">
         <v>1</v>
       </c>
@@ -6567,7 +6611,11 @@
       <c r="L101" t="n">
         <v>5</v>
       </c>
-      <c r="M101" t="inlineStr"/>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>항상 좋습니다</t>
+        </is>
+      </c>
       <c r="N101" t="b">
         <v>0</v>
       </c>
@@ -7175,7 +7223,11 @@
       <c r="L111" t="n">
         <v>5</v>
       </c>
-      <c r="M111" t="inlineStr"/>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>감사합니다</t>
+        </is>
+      </c>
       <c r="N111" t="b">
         <v>1</v>
       </c>
@@ -7235,7 +7287,11 @@
       <c r="L112" t="n">
         <v>4</v>
       </c>
-      <c r="M112" t="inlineStr"/>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>수강생 간의 친목 소음이 라운지에서 너무 크게 들립니다.</t>
+        </is>
+      </c>
       <c r="N112" t="b">
         <v>1</v>
       </c>
@@ -7659,7 +7715,11 @@
       <c r="L119" t="n">
         <v>5</v>
       </c>
-      <c r="M119" t="inlineStr"/>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>상담 신청을 남겼는데 운영팀에서 며칠째 확인을 안 하네요.</t>
+        </is>
+      </c>
       <c r="N119" t="b">
         <v>1</v>
       </c>
@@ -9483,7 +9543,11 @@
       <c r="L149" t="n">
         <v>5</v>
       </c>
-      <c r="M149" t="inlineStr"/>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>교육 프로그램 안내가 더 자주 나가면 좋을 것 같아요</t>
+        </is>
+      </c>
       <c r="N149" t="b">
         <v>0</v>
       </c>
@@ -10035,7 +10099,11 @@
       <c r="L158" t="n">
         <v>5</v>
       </c>
-      <c r="M158" t="inlineStr"/>
+      <c r="M158" t="inlineStr">
+        <is>
+          <t>이용방법이 직관적이지 않아요</t>
+        </is>
+      </c>
       <c r="N158" t="b">
         <v>0</v>
       </c>
@@ -10275,7 +10343,11 @@
       <c r="L162" t="n">
         <v>4</v>
       </c>
-      <c r="M162" t="inlineStr"/>
+      <c r="M162" t="inlineStr">
+        <is>
+          <t>이용방법이 직관적이지 않아요</t>
+        </is>
+      </c>
       <c r="N162" t="b">
         <v>0</v>
       </c>
@@ -11067,7 +11139,11 @@
       <c r="L175" t="n">
         <v>5</v>
       </c>
-      <c r="M175" t="inlineStr"/>
+      <c r="M175" t="inlineStr">
+        <is>
+          <t>출결 시스템이 자꾸 오류 나서 매번 수동으로 확인하는 게 번거롭습니다.</t>
+        </is>
+      </c>
       <c r="N175" t="b">
         <v>1</v>
       </c>
@@ -11863,7 +11939,11 @@
       <c r="L188" t="n">
         <v>5</v>
       </c>
-      <c r="M188" t="inlineStr"/>
+      <c r="M188" t="inlineStr">
+        <is>
+          <t xml:space="preserve">수강 신청여부를 빠르게 확인할 수 있으면 좋겠어요 </t>
+        </is>
+      </c>
       <c r="N188" t="b">
         <v>1</v>
       </c>
@@ -12479,7 +12559,11 @@
       <c r="L198" t="n">
         <v>5</v>
       </c>
-      <c r="M198" t="inlineStr"/>
+      <c r="M198" t="inlineStr">
+        <is>
+          <t>교육 프로그램 안내가 더 자주 나가면 좋을 것 같아요</t>
+        </is>
+      </c>
       <c r="N198" t="b">
         <v>1</v>
       </c>
@@ -13575,7 +13659,11 @@
       <c r="L216" t="n">
         <v>5</v>
       </c>
-      <c r="M216" t="inlineStr"/>
+      <c r="M216" t="inlineStr">
+        <is>
+          <t>강의실 조명이 너무 밝아서 화면을 볼 때 눈이 쉽게 피로해집니다.</t>
+        </is>
+      </c>
       <c r="N216" t="b">
         <v>0</v>
       </c>
@@ -13755,7 +13843,11 @@
       <c r="L219" t="n">
         <v>4</v>
       </c>
-      <c r="M219" t="inlineStr"/>
+      <c r="M219" t="inlineStr">
+        <is>
+          <t>찾아오는 길 안내가 부족해요</t>
+        </is>
+      </c>
       <c r="N219" t="b">
         <v>0</v>
       </c>
@@ -14187,7 +14279,11 @@
       <c r="L226" t="n">
         <v>5</v>
       </c>
-      <c r="M226" t="inlineStr"/>
+      <c r="M226" t="inlineStr">
+        <is>
+          <t>수강 신청여부를 빠르게 확인할 수 있으면 좋겠어요</t>
+        </is>
+      </c>
       <c r="N226" t="b">
         <v>1</v>
       </c>
@@ -15111,7 +15207,11 @@
       <c r="L241" t="n">
         <v>5</v>
       </c>
-      <c r="M241" t="inlineStr"/>
+      <c r="M241" t="inlineStr">
+        <is>
+          <t>강의실 조명이 너무 밝아서 화면을 볼 때 눈이 쉽게 피로해집니다.</t>
+        </is>
+      </c>
       <c r="N241" t="b">
         <v>0</v>
       </c>
@@ -15415,7 +15515,11 @@
       <c r="L246" t="n">
         <v>5</v>
       </c>
-      <c r="M246" t="inlineStr"/>
+      <c r="M246" t="inlineStr">
+        <is>
+          <t>상담 신청을 남겼는데 운영팀에서 며칠째 확인을 안 하네요.</t>
+        </is>
+      </c>
       <c r="N246" t="b">
         <v>1</v>
       </c>
@@ -15843,7 +15947,11 @@
       <c r="L253" t="n">
         <v>4</v>
       </c>
-      <c r="M253" t="inlineStr"/>
+      <c r="M253" t="inlineStr">
+        <is>
+          <t>화장실 청소 상태가 별로라 이용할 때마다 불편해요.</t>
+        </is>
+      </c>
       <c r="N253" t="b">
         <v>1</v>
       </c>
@@ -16203,7 +16311,11 @@
       <c r="L259" t="n">
         <v>5</v>
       </c>
-      <c r="M259" t="inlineStr"/>
+      <c r="M259" t="inlineStr">
+        <is>
+          <t>교육 프로그램 안내가 더 자주 나가면 좋을 것 같아요</t>
+        </is>
+      </c>
       <c r="N259" t="b">
         <v>0</v>
       </c>
@@ -17471,7 +17583,11 @@
       <c r="L280" t="n">
         <v>5</v>
       </c>
-      <c r="M280" t="inlineStr"/>
+      <c r="M280" t="inlineStr">
+        <is>
+          <t>안내문이 센터 내 잘 보이는 곳이 붙어 있으면 좋겠어요.</t>
+        </is>
+      </c>
       <c r="N280" t="b">
         <v>1</v>
       </c>
@@ -19111,7 +19227,11 @@
       <c r="L307" t="n">
         <v>5</v>
       </c>
-      <c r="M307" t="inlineStr"/>
+      <c r="M307" t="inlineStr">
+        <is>
+          <t>찾아오는 길 안내가 부족해요</t>
+        </is>
+      </c>
       <c r="N307" t="b">
         <v>1</v>
       </c>
@@ -19291,7 +19411,11 @@
       <c r="L310" t="n">
         <v>4</v>
       </c>
-      <c r="M310" t="inlineStr"/>
+      <c r="M310" t="inlineStr">
+        <is>
+          <t>교육 프로그램 안내가 더 자주 나가면 좋을 것 같아요</t>
+        </is>
+      </c>
       <c r="N310" t="b">
         <v>0</v>
       </c>
@@ -20947,7 +21071,11 @@
       <c r="L337" t="n">
         <v>4</v>
       </c>
-      <c r="M337" t="inlineStr"/>
+      <c r="M337" t="inlineStr">
+        <is>
+          <t>상담 신청을 남겼는데 운영팀에서 며칠째 확인을 안 하네요.</t>
+        </is>
+      </c>
       <c r="N337" t="b">
         <v>0</v>
       </c>
@@ -22099,7 +22227,11 @@
       <c r="L356" t="n">
         <v>5</v>
       </c>
-      <c r="M356" t="inlineStr"/>
+      <c r="M356" t="inlineStr">
+        <is>
+          <t>화장실 청소 상태가 별로라 이용할 때마다 불편해요.</t>
+        </is>
+      </c>
       <c r="N356" t="b">
         <v>1</v>
       </c>
@@ -24955,7 +25087,11 @@
       <c r="L403" t="n">
         <v>5</v>
       </c>
-      <c r="M403" t="inlineStr"/>
+      <c r="M403" t="inlineStr">
+        <is>
+          <t>비상구 쪽에 짐이 쌓여 있어서 안전 문제가 걱정돼요.</t>
+        </is>
+      </c>
       <c r="N403" t="b">
         <v>1</v>
       </c>
@@ -25743,7 +25879,11 @@
       <c r="L416" t="n">
         <v>4</v>
       </c>
-      <c r="M416" t="inlineStr"/>
+      <c r="M416" t="inlineStr">
+        <is>
+          <t>라운지를 써도 되는지 모르겠어요</t>
+        </is>
+      </c>
       <c r="N416" t="b">
         <v>1</v>
       </c>
@@ -26103,7 +26243,11 @@
       <c r="L422" t="n">
         <v>4</v>
       </c>
-      <c r="M422" t="inlineStr"/>
+      <c r="M422" t="inlineStr">
+        <is>
+          <t>비상구 쪽에 짐이 쌓여 있어서 안전 문제가 걱정돼요.</t>
+        </is>
+      </c>
       <c r="N422" t="b">
         <v>1</v>
       </c>
@@ -26587,7 +26731,11 @@
       <c r="L430" t="n">
         <v>5</v>
       </c>
-      <c r="M430" t="inlineStr"/>
+      <c r="M430" t="inlineStr">
+        <is>
+          <t>실습용 데이터나 서버 접속이 원활하지 않을 때가 많습니다.</t>
+        </is>
+      </c>
       <c r="N430" t="b">
         <v>0</v>
       </c>
@@ -27195,7 +27343,11 @@
       <c r="L440" t="n">
         <v>5</v>
       </c>
-      <c r="M440" t="inlineStr"/>
+      <c r="M440" t="inlineStr">
+        <is>
+          <t>수강생 간의 친목 소음이 라운지에서 너무 크게 들립니다.</t>
+        </is>
+      </c>
       <c r="N440" t="b">
         <v>1</v>
       </c>
@@ -28111,7 +28263,11 @@
       <c r="L455" t="n">
         <v>5</v>
       </c>
-      <c r="M455" t="inlineStr"/>
+      <c r="M455" t="inlineStr">
+        <is>
+          <t>프로그램 종류랑 난이도가 조정되면 좋을 것 같아요</t>
+        </is>
+      </c>
       <c r="N455" t="b">
         <v>1</v>
       </c>
@@ -28295,7 +28451,11 @@
       <c r="L458" t="n">
         <v>5</v>
       </c>
-      <c r="M458" t="inlineStr"/>
+      <c r="M458" t="inlineStr">
+        <is>
+          <t>비상구 쪽에 짐이 쌓여 있어서 안전 문제가 걱정돼요.</t>
+        </is>
+      </c>
       <c r="N458" t="b">
         <v>1</v>
       </c>
@@ -28475,7 +28635,11 @@
       <c r="L461" t="n">
         <v>5</v>
       </c>
-      <c r="M461" t="inlineStr"/>
+      <c r="M461" t="inlineStr">
+        <is>
+          <t>출결 시스템이 자꾸 오류 나서 매번 수동으로 확인하는 게 번거롭습니다.</t>
+        </is>
+      </c>
       <c r="N461" t="b">
         <v>1</v>
       </c>
@@ -28595,7 +28759,11 @@
       <c r="L463" t="n">
         <v>5</v>
       </c>
-      <c r="M463" t="inlineStr"/>
+      <c r="M463" t="inlineStr">
+        <is>
+          <t>출결 시스템이 자꾸 오류 나서 매번 수동으로 확인하는 게 번거롭습니다.</t>
+        </is>
+      </c>
       <c r="N463" t="b">
         <v>1</v>
       </c>
@@ -28779,7 +28947,11 @@
       <c r="L466" t="n">
         <v>5</v>
       </c>
-      <c r="M466" t="inlineStr"/>
+      <c r="M466" t="inlineStr">
+        <is>
+          <t>운영 안내 시각 변경된 거 공지해주세요</t>
+        </is>
+      </c>
       <c r="N466" t="b">
         <v>1</v>
       </c>
@@ -28899,7 +29071,11 @@
       <c r="L468" t="n">
         <v>4</v>
       </c>
-      <c r="M468" t="inlineStr"/>
+      <c r="M468" t="inlineStr">
+        <is>
+          <t>운영 안내 시각 변경된 거 공지해주세요</t>
+        </is>
+      </c>
       <c r="N468" t="b">
         <v>1</v>
       </c>
@@ -29019,7 +29195,11 @@
       <c r="L470" t="n">
         <v>4</v>
       </c>
-      <c r="M470" t="inlineStr"/>
+      <c r="M470" t="inlineStr">
+        <is>
+          <t xml:space="preserve">수강 신청여부를 빠르게 확인할 수 있으면 좋겠어요 </t>
+        </is>
+      </c>
       <c r="N470" t="b">
         <v>1</v>
       </c>
@@ -29383,7 +29563,11 @@
       <c r="L476" t="n">
         <v>5</v>
       </c>
-      <c r="M476" t="inlineStr"/>
+      <c r="M476" t="inlineStr">
+        <is>
+          <t>안내문이 센터 내 잘 보이는 곳이 붙어 있으면 좋겠어요.</t>
+        </is>
+      </c>
       <c r="N476" t="b">
         <v>1</v>
       </c>
@@ -29627,7 +29811,11 @@
       <c r="L480" t="n">
         <v>5</v>
       </c>
-      <c r="M480" t="inlineStr"/>
+      <c r="M480" t="inlineStr">
+        <is>
+          <t>안내문이 센터 내 잘 보이는 곳이 붙어 있으면 좋겠어요.</t>
+        </is>
+      </c>
       <c r="N480" t="b">
         <v>0</v>
       </c>
@@ -29931,7 +30119,11 @@
       <c r="L485" t="n">
         <v>5</v>
       </c>
-      <c r="M485" t="inlineStr"/>
+      <c r="M485" t="inlineStr">
+        <is>
+          <t>프로그램 난이도 조정이 필요할 것 같아요</t>
+        </is>
+      </c>
       <c r="N485" t="b">
         <v>1</v>
       </c>
@@ -30655,7 +30847,11 @@
       <c r="L497" t="n">
         <v>5</v>
       </c>
-      <c r="M497" t="inlineStr"/>
+      <c r="M497" t="inlineStr">
+        <is>
+          <t>이용 안내가 좀 구체적이면 좋을 것 같아요</t>
+        </is>
+      </c>
       <c r="N497" t="b">
         <v>0</v>
       </c>
@@ -31619,7 +31815,11 @@
       <c r="L513" t="n">
         <v>5</v>
       </c>
-      <c r="M513" t="inlineStr"/>
+      <c r="M513" t="inlineStr">
+        <is>
+          <t xml:space="preserve">수강 신청여부를 빠르게 확인할 수 있으면 좋겠어요 </t>
+        </is>
+      </c>
       <c r="N513" t="b">
         <v>1</v>
       </c>
@@ -31923,7 +32123,11 @@
       <c r="L518" t="n">
         <v>5</v>
       </c>
-      <c r="M518" t="inlineStr"/>
+      <c r="M518" t="inlineStr">
+        <is>
+          <t>안내문이 센터 내 잘 보이는 곳이 붙어 있으면 좋겠어요.</t>
+        </is>
+      </c>
       <c r="N518" t="b">
         <v>1</v>
       </c>
@@ -32283,7 +32487,11 @@
       <c r="L524" t="n">
         <v>4</v>
       </c>
-      <c r="M524" t="inlineStr"/>
+      <c r="M524" t="inlineStr">
+        <is>
+          <t>수강생 간의 친목 소음이 라운지에서 너무 크게 들립니다.</t>
+        </is>
+      </c>
       <c r="N524" t="b">
         <v>1</v>
       </c>
@@ -33683,7 +33891,11 @@
       <c r="L547" t="n">
         <v>5</v>
       </c>
-      <c r="M547" t="inlineStr"/>
+      <c r="M547" t="inlineStr">
+        <is>
+          <t>안내문이 센터 내 잘 보이는 곳이 붙어 있으면 좋겠어요.</t>
+        </is>
+      </c>
       <c r="N547" t="b">
         <v>0</v>
       </c>
@@ -34283,7 +34495,11 @@
       <c r="L557" t="n">
         <v>4</v>
       </c>
-      <c r="M557" t="inlineStr"/>
+      <c r="M557" t="inlineStr">
+        <is>
+          <t>안내문이 센터 내 잘 보이는 곳이 붙어 있으면 좋겠어요.</t>
+        </is>
+      </c>
       <c r="N557" t="b">
         <v>1</v>
       </c>
@@ -34527,7 +34743,11 @@
       <c r="L561" t="n">
         <v>4</v>
       </c>
-      <c r="M561" t="inlineStr"/>
+      <c r="M561" t="inlineStr">
+        <is>
+          <t>상담 신청을 남겼는데 운영팀에서 며칠째 확인을 안 하네요.</t>
+        </is>
+      </c>
       <c r="N561" t="b">
         <v>1</v>
       </c>
@@ -34951,7 +35171,11 @@
       <c r="L568" t="n">
         <v>5</v>
       </c>
-      <c r="M568" t="inlineStr"/>
+      <c r="M568" t="inlineStr">
+        <is>
+          <t>출결 시스템이 자꾸 오류 나서 매번 수동으로 확인하는 게 번거롭습니다.</t>
+        </is>
+      </c>
       <c r="N568" t="b">
         <v>1</v>
       </c>
@@ -35979,7 +36203,11 @@
       <c r="L585" t="n">
         <v>4</v>
       </c>
-      <c r="M585" t="inlineStr"/>
+      <c r="M585" t="inlineStr">
+        <is>
+          <t>엘리베이터가 느려요</t>
+        </is>
+      </c>
       <c r="N585" t="b">
         <v>1</v>
       </c>
@@ -36403,7 +36631,11 @@
       <c r="L592" t="n">
         <v>5</v>
       </c>
-      <c r="M592" t="inlineStr"/>
+      <c r="M592" t="inlineStr">
+        <is>
+          <t>안내문이 센터 내 잘 보이는 곳이 붙어 있으면 좋겠어요.</t>
+        </is>
+      </c>
       <c r="N592" t="b">
         <v>0</v>
       </c>
@@ -36523,7 +36755,11 @@
       <c r="L594" t="n">
         <v>4</v>
       </c>
-      <c r="M594" t="inlineStr"/>
+      <c r="M594" t="inlineStr">
+        <is>
+          <t>좌석 배치도가 눈에 잘 보이면 좋겠어요</t>
+        </is>
+      </c>
       <c r="N594" t="b">
         <v>1</v>
       </c>
@@ -36583,7 +36819,11 @@
       <c r="L595" t="n">
         <v>4</v>
       </c>
-      <c r="M595" t="inlineStr"/>
+      <c r="M595" t="inlineStr">
+        <is>
+          <t>공간 세부 안내가 필요해요</t>
+        </is>
+      </c>
       <c r="N595" t="b">
         <v>1</v>
       </c>
@@ -37067,7 +37307,11 @@
       <c r="L603" t="n">
         <v>5</v>
       </c>
-      <c r="M603" t="inlineStr"/>
+      <c r="M603" t="inlineStr">
+        <is>
+          <t>갑작스러운 센터 휴관 공지가 너무 늦게 올라왔어요.</t>
+        </is>
+      </c>
       <c r="N603" t="b">
         <v>1</v>
       </c>
@@ -37371,7 +37615,11 @@
       <c r="L608" t="n">
         <v>5</v>
       </c>
-      <c r="M608" t="inlineStr"/>
+      <c r="M608" t="inlineStr">
+        <is>
+          <t>와이파이가 자꾸 끊겨서 개인 노트북으로 작업하기 힘듭니다.</t>
+        </is>
+      </c>
       <c r="N608" t="b">
         <v>1</v>
       </c>
@@ -37927,7 +38175,11 @@
       <c r="L617" t="n">
         <v>5</v>
       </c>
-      <c r="M617" t="inlineStr"/>
+      <c r="M617" t="inlineStr">
+        <is>
+          <t>최신 PC가 더 있으면 좋겠어요</t>
+        </is>
+      </c>
       <c r="N617" t="b">
         <v>0</v>
       </c>
@@ -38115,7 +38367,11 @@
       <c r="L620" t="n">
         <v>5</v>
       </c>
-      <c r="M620" t="inlineStr"/>
+      <c r="M620" t="inlineStr">
+        <is>
+          <t>최신 PC가 더 있으면 좋겠어요</t>
+        </is>
+      </c>
       <c r="N620" t="b">
         <v>0</v>
       </c>
@@ -38299,7 +38555,11 @@
       <c r="L623" t="n">
         <v>5</v>
       </c>
-      <c r="M623" t="inlineStr"/>
+      <c r="M623" t="inlineStr">
+        <is>
+          <t>프로그램 난이도 조정이 필요할 것 같아요</t>
+        </is>
+      </c>
       <c r="N623" t="b">
         <v>1</v>
       </c>
@@ -38483,7 +38743,11 @@
       <c r="L626" t="n">
         <v>5</v>
       </c>
-      <c r="M626" t="inlineStr"/>
+      <c r="M626" t="inlineStr">
+        <is>
+          <t>어떻게 찾아오는지 잘 모르겠어요</t>
+        </is>
+      </c>
       <c r="N626" t="b">
         <v>0</v>
       </c>
@@ -38663,7 +38927,11 @@
       <c r="L629" t="n">
         <v>5</v>
       </c>
-      <c r="M629" t="inlineStr"/>
+      <c r="M629" t="inlineStr">
+        <is>
+          <t xml:space="preserve">수강 신청여부를 빠르게 확인할 수 있으면 좋겠어요 </t>
+        </is>
+      </c>
       <c r="N629" t="b">
         <v>1</v>
       </c>
@@ -38907,7 +39175,11 @@
       <c r="L633" t="n">
         <v>4</v>
       </c>
-      <c r="M633" t="inlineStr"/>
+      <c r="M633" t="inlineStr">
+        <is>
+          <t>출결 시스템이 자꾸 오류 나서 매번 수동으로 확인하는 게 번거롭습니다.</t>
+        </is>
+      </c>
       <c r="N633" t="b">
         <v>1</v>
       </c>
@@ -38967,7 +39239,11 @@
       <c r="L634" t="n">
         <v>4</v>
       </c>
-      <c r="M634" t="inlineStr"/>
+      <c r="M634" t="inlineStr">
+        <is>
+          <t>수강생 간의 친목 소음이 라운지에서 너무 크게 들립니다.</t>
+        </is>
+      </c>
       <c r="N634" t="b">
         <v>1</v>
       </c>
@@ -39027,7 +39303,11 @@
       <c r="L635" t="n">
         <v>5</v>
       </c>
-      <c r="M635" t="inlineStr"/>
+      <c r="M635" t="inlineStr">
+        <is>
+          <t>잘 쓰고 있어요 감사합니다.</t>
+        </is>
+      </c>
       <c r="N635" t="b">
         <v>0</v>
       </c>
@@ -39147,7 +39427,11 @@
       <c r="L637" t="n">
         <v>5</v>
       </c>
-      <c r="M637" t="inlineStr"/>
+      <c r="M637" t="inlineStr">
+        <is>
+          <t>전자기기 사용 방법을 안내해주면 좋겠어요</t>
+        </is>
+      </c>
       <c r="N637" t="b">
         <v>1</v>
       </c>
@@ -39267,7 +39551,11 @@
       <c r="L639" t="n">
         <v>5</v>
       </c>
-      <c r="M639" t="inlineStr"/>
+      <c r="M639" t="inlineStr">
+        <is>
+          <t>전자기기 사용 방법을 안내해주면 좋겠어요</t>
+        </is>
+      </c>
       <c r="N639" t="b">
         <v>1</v>
       </c>
@@ -39507,7 +39795,11 @@
       <c r="L643" t="n">
         <v>5</v>
       </c>
-      <c r="M643" t="inlineStr"/>
+      <c r="M643" t="inlineStr">
+        <is>
+          <t>수강 신청여부를 빠르게 확인할 수 있으면 좋겠어요</t>
+        </is>
+      </c>
       <c r="N643" t="b">
         <v>1</v>
       </c>
@@ -39875,7 +40167,11 @@
       <c r="L649" t="n">
         <v>4</v>
       </c>
-      <c r="M649" t="inlineStr"/>
+      <c r="M649" t="inlineStr">
+        <is>
+          <t>동선이 복잡해요</t>
+        </is>
+      </c>
       <c r="N649" t="b">
         <v>1</v>
       </c>
@@ -40239,7 +40535,11 @@
       <c r="L655" t="n">
         <v>5</v>
       </c>
-      <c r="M655" t="inlineStr"/>
+      <c r="M655" t="inlineStr">
+        <is>
+          <t>안내문이 센터 내 잘 보이는 곳이 붙어 있으면 좋겠어요.</t>
+        </is>
+      </c>
       <c r="N655" t="b">
         <v>1</v>
       </c>
@@ -40299,7 +40599,11 @@
       <c r="L656" t="n">
         <v>4</v>
       </c>
-      <c r="M656" t="inlineStr"/>
+      <c r="M656" t="inlineStr">
+        <is>
+          <t>갑작스러운 센터 휴관 공지가 너무 늦게 올라왔어요.</t>
+        </is>
+      </c>
       <c r="N656" t="b">
         <v>1</v>
       </c>
@@ -40663,7 +40967,11 @@
       <c r="L662" t="n">
         <v>4</v>
       </c>
-      <c r="M662" t="inlineStr"/>
+      <c r="M662" t="inlineStr">
+        <is>
+          <t>교육 프로그램 안내가 더 자주 나가면 좋을 것 같아요</t>
+        </is>
+      </c>
       <c r="N662" t="b">
         <v>1</v>
       </c>
@@ -41207,7 +41515,11 @@
       <c r="L671" t="n">
         <v>5</v>
       </c>
-      <c r="M671" t="inlineStr"/>
+      <c r="M671" t="inlineStr">
+        <is>
+          <t>라운지 사용해도 되는지 모르겠어요</t>
+        </is>
+      </c>
       <c r="N671" t="b">
         <v>1</v>
       </c>
@@ -41451,7 +41763,11 @@
       <c r="L675" t="n">
         <v>5</v>
       </c>
-      <c r="M675" t="inlineStr"/>
+      <c r="M675" t="inlineStr">
+        <is>
+          <t>찾아오는 길 안내가 부족해요</t>
+        </is>
+      </c>
       <c r="N675" t="b">
         <v>1</v>
       </c>
@@ -42547,7 +42863,11 @@
       <c r="L693" t="n">
         <v>4</v>
       </c>
-      <c r="M693" t="inlineStr"/>
+      <c r="M693" t="inlineStr">
+        <is>
+          <t>찾아오는 길 안내가 부족해요</t>
+        </is>
+      </c>
       <c r="N693" t="b">
         <v>1</v>
       </c>
@@ -42791,7 +43111,11 @@
       <c r="L697" t="n">
         <v>5</v>
       </c>
-      <c r="M697" t="inlineStr"/>
+      <c r="M697" t="inlineStr">
+        <is>
+          <t>교육 프로그램 안내가 더 자주 나가면 좋을 것 같아요</t>
+        </is>
+      </c>
       <c r="N697" t="b">
         <v>0</v>
       </c>
@@ -43151,7 +43475,11 @@
       <c r="L703" t="n">
         <v>5</v>
       </c>
-      <c r="M703" t="inlineStr"/>
+      <c r="M703" t="inlineStr">
+        <is>
+          <t>자주 잘 쓰고 있어요 ㅎㅎ</t>
+        </is>
+      </c>
       <c r="N703" t="b">
         <v>0</v>
       </c>
@@ -43211,7 +43539,11 @@
       <c r="L704" t="n">
         <v>4</v>
       </c>
-      <c r="M704" t="inlineStr"/>
+      <c r="M704" t="inlineStr">
+        <is>
+          <t>프로그램 난이도 조정이 필요할 것 같아요</t>
+        </is>
+      </c>
       <c r="N704" t="b">
         <v>1</v>
       </c>
@@ -43395,7 +43727,11 @@
       <c r="L707" t="n">
         <v>5</v>
       </c>
-      <c r="M707" t="inlineStr"/>
+      <c r="M707" t="inlineStr">
+        <is>
+          <t>강의실 조명이 너무 밝아서 화면을 볼 때 눈이 쉽게 피로해집니다.</t>
+        </is>
+      </c>
       <c r="N707" t="b">
         <v>1</v>
       </c>
@@ -44007,7 +44343,11 @@
       <c r="L717" t="n">
         <v>4</v>
       </c>
-      <c r="M717" t="inlineStr"/>
+      <c r="M717" t="inlineStr">
+        <is>
+          <t>비상구 쪽에 짐이 쌓여 있어서 안전 문제가 걱정돼요.</t>
+        </is>
+      </c>
       <c r="N717" t="b">
         <v>1</v>
       </c>
@@ -44375,7 +44715,11 @@
       <c r="L723" t="n">
         <v>5</v>
       </c>
-      <c r="M723" t="inlineStr"/>
+      <c r="M723" t="inlineStr">
+        <is>
+          <t>찾아오는 길 안내가 부족해요</t>
+        </is>
+      </c>
       <c r="N723" t="b">
         <v>1</v>
       </c>
@@ -44975,7 +45319,11 @@
       <c r="L733" t="n">
         <v>5</v>
       </c>
-      <c r="M733" t="inlineStr"/>
+      <c r="M733" t="inlineStr">
+        <is>
+          <t>안내문이 센터 내 잘 보이는 곳이 붙어 있으면 좋겠어요.</t>
+        </is>
+      </c>
       <c r="N733" t="b">
         <v>1</v>
       </c>
@@ -45539,7 +45887,11 @@
       <c r="L742" t="n">
         <v>5</v>
       </c>
-      <c r="M742" t="inlineStr"/>
+      <c r="M742" t="inlineStr">
+        <is>
+          <t>좋아요</t>
+        </is>
+      </c>
       <c r="N742" t="b">
         <v>0</v>
       </c>
@@ -45599,7 +45951,11 @@
       <c r="L743" t="n">
         <v>4</v>
       </c>
-      <c r="M743" t="inlineStr"/>
+      <c r="M743" t="inlineStr">
+        <is>
+          <t>시설이 좋긴 한데, 예약 방법을 잘 모르겠어요</t>
+        </is>
+      </c>
       <c r="N743" t="b">
         <v>0</v>
       </c>
@@ -46087,7 +46443,11 @@
       <c r="L751" t="n">
         <v>4</v>
       </c>
-      <c r="M751" t="inlineStr"/>
+      <c r="M751" t="inlineStr">
+        <is>
+          <t>친절하십니다!</t>
+        </is>
+      </c>
       <c r="N751" t="b">
         <v>0</v>
       </c>
@@ -47451,7 +47811,11 @@
       <c r="L775" t="n">
         <v>5</v>
       </c>
-      <c r="M775" t="inlineStr"/>
+      <c r="M775" t="inlineStr">
+        <is>
+          <t>안내문이 센터 내 잘 보이는 곳이 붙어 있으면 좋겠어요.</t>
+        </is>
+      </c>
       <c r="N775" t="b">
         <v>1</v>
       </c>
@@ -48183,7 +48547,11 @@
       <c r="L788" t="n">
         <v>4</v>
       </c>
-      <c r="M788" t="inlineStr"/>
+      <c r="M788" t="inlineStr">
+        <is>
+          <t>출결 시스템이 자꾸 오류 나서 매번 수동으로 확인하는 게 번거롭습니다.</t>
+        </is>
+      </c>
       <c r="N788" t="b">
         <v>1</v>
       </c>
@@ -48815,7 +49183,11 @@
       <c r="L799" t="n">
         <v>4</v>
       </c>
-      <c r="M799" t="inlineStr"/>
+      <c r="M799" t="inlineStr">
+        <is>
+          <t>수강생 간의 친목 소음이 라운지에서 너무 크게 들립니다.</t>
+        </is>
+      </c>
       <c r="N799" t="b">
         <v>0</v>
       </c>
@@ -49887,7 +50259,11 @@
       <c r="L818" t="n">
         <v>5</v>
       </c>
-      <c r="M818" t="inlineStr"/>
+      <c r="M818" t="inlineStr">
+        <is>
+          <t>프로그램 난이도 조정이 필요할 것 같아요</t>
+        </is>
+      </c>
       <c r="N818" t="b">
         <v>0</v>
       </c>
@@ -49999,7 +50375,11 @@
       <c r="L820" t="n">
         <v>4</v>
       </c>
-      <c r="M820" t="inlineStr"/>
+      <c r="M820" t="inlineStr">
+        <is>
+          <t>운영 안내 시각 변경된 거 공지해주세요</t>
+        </is>
+      </c>
       <c r="N820" t="b">
         <v>0</v>
       </c>
@@ -51083,7 +51463,11 @@
       <c r="L839" t="n">
         <v>5</v>
       </c>
-      <c r="M839" t="inlineStr"/>
+      <c r="M839" t="inlineStr">
+        <is>
+          <t>찾아오는 길 안내가 부족해요</t>
+        </is>
+      </c>
       <c r="N839" t="b">
         <v>0</v>
       </c>
@@ -52279,7 +52663,11 @@
       <c r="L860" t="n">
         <v>4</v>
       </c>
-      <c r="M860" t="inlineStr"/>
+      <c r="M860" t="inlineStr">
+        <is>
+          <t>친절하십니다 ㅎㅎ</t>
+        </is>
+      </c>
       <c r="N860" t="b">
         <v>1</v>
       </c>
@@ -53639,7 +54027,11 @@
       <c r="L884" t="n">
         <v>4</v>
       </c>
-      <c r="M884" t="inlineStr"/>
+      <c r="M884" t="inlineStr">
+        <is>
+          <t>찾아오는 길 안내가 부족해요</t>
+        </is>
+      </c>
       <c r="N884" t="b">
         <v>0</v>
       </c>
@@ -54035,7 +54427,11 @@
       <c r="L891" t="n">
         <v>5</v>
       </c>
-      <c r="M891" t="inlineStr"/>
+      <c r="M891" t="inlineStr">
+        <is>
+          <t>비상구 쪽에 짐이 쌓여 있어서 안전 문제가 걱정돼요.</t>
+        </is>
+      </c>
       <c r="N891" t="b">
         <v>0</v>
       </c>
@@ -55123,7 +55519,11 @@
       <c r="L910" t="n">
         <v>4</v>
       </c>
-      <c r="M910" t="inlineStr"/>
+      <c r="M910" t="inlineStr">
+        <is>
+          <t>운영시간이 자주 바뀌는 것 같아요</t>
+        </is>
+      </c>
       <c r="N910" t="b">
         <v>0</v>
       </c>
@@ -55347,7 +55747,11 @@
       <c r="L914" t="n">
         <v>5</v>
       </c>
-      <c r="M914" t="inlineStr"/>
+      <c r="M914" t="inlineStr">
+        <is>
+          <t>이용방법이 직관적이지 않아요</t>
+        </is>
+      </c>
       <c r="N914" t="b">
         <v>1</v>
       </c>
@@ -55803,7 +56207,11 @@
       <c r="L922" t="n">
         <v>5</v>
       </c>
-      <c r="M922" t="inlineStr"/>
+      <c r="M922" t="inlineStr">
+        <is>
+          <t>상담 신청을 남겼는데 운영팀에서 며칠째 확인을 안 하네요.</t>
+        </is>
+      </c>
       <c r="N922" t="b">
         <v>0</v>
       </c>
@@ -56151,7 +56559,11 @@
       <c r="L928" t="n">
         <v>5</v>
       </c>
-      <c r="M928" t="inlineStr"/>
+      <c r="M928" t="inlineStr">
+        <is>
+          <t>예약 시스템을 사용하기 어려워요</t>
+        </is>
+      </c>
       <c r="N928" t="b">
         <v>1</v>
       </c>
@@ -57003,7 +57415,11 @@
       <c r="L943" t="n">
         <v>5</v>
       </c>
-      <c r="M943" t="inlineStr"/>
+      <c r="M943" t="inlineStr">
+        <is>
+          <t>휴식 취할 수 있는 공간이 더 많으면 좋겠어요</t>
+        </is>
+      </c>
       <c r="N943" t="b">
         <v>0</v>
       </c>
@@ -57791,7 +58207,11 @@
       <c r="L957" t="n">
         <v>5</v>
       </c>
-      <c r="M957" t="inlineStr"/>
+      <c r="M957" t="inlineStr">
+        <is>
+          <t>상담 신청을 남겼는데 운영팀에서 며칠째 확인을 안 하네요.</t>
+        </is>
+      </c>
       <c r="N957" t="b">
         <v>1</v>
       </c>
@@ -57959,7 +58379,11 @@
       <c r="L960" t="n">
         <v>5</v>
       </c>
-      <c r="M960" t="inlineStr"/>
+      <c r="M960" t="inlineStr">
+        <is>
+          <t>이용방법이 직관적이지 않아요</t>
+        </is>
+      </c>
       <c r="N960" t="b">
         <v>0</v>
       </c>
@@ -58127,7 +58551,11 @@
       <c r="L963" t="n">
         <v>5</v>
       </c>
-      <c r="M963" t="inlineStr"/>
+      <c r="M963" t="inlineStr">
+        <is>
+          <t>찾아오는 길 안내가 부족해요</t>
+        </is>
+      </c>
       <c r="N963" t="b">
         <v>0</v>
       </c>
@@ -58183,7 +58611,11 @@
       <c r="L964" t="n">
         <v>5</v>
       </c>
-      <c r="M964" t="inlineStr"/>
+      <c r="M964" t="inlineStr">
+        <is>
+          <t>라운지를 써도 되는지 잘 모르겠어요</t>
+        </is>
+      </c>
       <c r="N964" t="b">
         <v>0</v>
       </c>
@@ -58803,7 +59235,11 @@
       <c r="L975" t="n">
         <v>4</v>
       </c>
-      <c r="M975" t="inlineStr"/>
+      <c r="M975" t="inlineStr">
+        <is>
+          <t>문의를 어디다가 해야되는지 모르겠어요</t>
+        </is>
+      </c>
       <c r="N975" t="b">
         <v>0</v>
       </c>
@@ -59031,7 +59467,11 @@
       <c r="L979" t="n">
         <v>4</v>
       </c>
-      <c r="M979" t="inlineStr"/>
+      <c r="M979" t="inlineStr">
+        <is>
+          <t>더 다양한 행사를 하면 좋을 것 같아요</t>
+        </is>
+      </c>
       <c r="N979" t="b">
         <v>0</v>
       </c>
